--- a/data/nzd0589/nzd0589.xlsx
+++ b/data/nzd0589/nzd0589.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J479"/>
+  <dimension ref="A1:J482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>333.49</v>
+        <v>345.47</v>
       </c>
       <c r="C479" t="n">
         <v>212.5</v>
@@ -17678,6 +17678,114 @@
         <v>196.62</v>
       </c>
       <c r="J479" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:47+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>343.94</v>
+      </c>
+      <c r="C480" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="D480" t="n">
+        <v>240.14</v>
+      </c>
+      <c r="E480" t="n">
+        <v>216.52</v>
+      </c>
+      <c r="F480" t="n">
+        <v>204</v>
+      </c>
+      <c r="G480" t="n">
+        <v>221.86</v>
+      </c>
+      <c r="H480" t="n">
+        <v>207.84</v>
+      </c>
+      <c r="I480" t="n">
+        <v>196.91</v>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:43+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>343.94</v>
+      </c>
+      <c r="C481" t="n">
+        <v>212.99</v>
+      </c>
+      <c r="D481" t="n">
+        <v>241.28</v>
+      </c>
+      <c r="E481" t="n">
+        <v>216.92</v>
+      </c>
+      <c r="F481" t="n">
+        <v>205.88</v>
+      </c>
+      <c r="G481" t="n">
+        <v>223.56</v>
+      </c>
+      <c r="H481" t="n">
+        <v>209.13</v>
+      </c>
+      <c r="I481" t="n">
+        <v>198.38</v>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>343.07</v>
+      </c>
+      <c r="C482" t="n">
+        <v>212.99</v>
+      </c>
+      <c r="D482" t="n">
+        <v>241.28</v>
+      </c>
+      <c r="E482" t="n">
+        <v>216.92</v>
+      </c>
+      <c r="F482" t="n">
+        <v>205.88</v>
+      </c>
+      <c r="G482" t="n">
+        <v>223.56</v>
+      </c>
+      <c r="H482" t="n">
+        <v>209.13</v>
+      </c>
+      <c r="I482" t="n">
+        <v>198.76</v>
+      </c>
+      <c r="J482" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17694,7 +17802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B515"/>
+  <dimension ref="A1:B518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22847,6 +22955,36 @@
       </c>
       <c r="B515" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -23009,28 +23147,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1384833802092909</v>
+        <v>0.1511170470406395</v>
       </c>
       <c r="J2" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K2" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002094001539445278</v>
+        <v>0.002524696919292135</v>
       </c>
       <c r="M2" t="n">
-        <v>15.60291647500164</v>
+        <v>15.52800827848677</v>
       </c>
       <c r="N2" t="n">
-        <v>523.8531937526044</v>
+        <v>520.9497071787575</v>
       </c>
       <c r="O2" t="n">
-        <v>22.88783942954434</v>
+        <v>22.82432271018699</v>
       </c>
       <c r="P2" t="n">
-        <v>333.3949826716623</v>
+        <v>333.2601692767869</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23081,28 +23219,28 @@
         <v>0.1473</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08698670846392632</v>
+        <v>0.08525480415182972</v>
       </c>
       <c r="J3" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K3" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0374561765387571</v>
+        <v>0.03646561522399649</v>
       </c>
       <c r="M3" t="n">
-        <v>2.627360844616057</v>
+        <v>2.618152461936709</v>
       </c>
       <c r="N3" t="n">
-        <v>11.15561113979986</v>
+        <v>11.09877136110579</v>
       </c>
       <c r="O3" t="n">
-        <v>3.340001667634294</v>
+        <v>3.331481856637642</v>
       </c>
       <c r="P3" t="n">
-        <v>211.9148782140603</v>
+        <v>211.9333795236228</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23153,28 +23291,28 @@
         <v>0.0717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.246604672510324</v>
+        <v>0.24261966435656</v>
       </c>
       <c r="J4" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K4" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08905886151563736</v>
+        <v>0.08737919735338762</v>
       </c>
       <c r="M4" t="n">
-        <v>4.390610965478223</v>
+        <v>4.3792305284438</v>
       </c>
       <c r="N4" t="n">
-        <v>35.35736699449625</v>
+        <v>35.2044419594378</v>
       </c>
       <c r="O4" t="n">
-        <v>5.946206100909743</v>
+        <v>5.933333123922657</v>
       </c>
       <c r="P4" t="n">
-        <v>237.5299502891237</v>
+        <v>237.5727338074621</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23225,28 +23363,28 @@
         <v>0.141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1249905744985465</v>
+        <v>0.1182872470367866</v>
       </c>
       <c r="J5" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K5" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06127720850539597</v>
+        <v>0.05522169789221987</v>
       </c>
       <c r="M5" t="n">
-        <v>2.933973402988374</v>
+        <v>2.945688666238718</v>
       </c>
       <c r="N5" t="n">
-        <v>13.700347769687</v>
+        <v>13.80448864465817</v>
       </c>
       <c r="O5" t="n">
-        <v>3.701398083114946</v>
+        <v>3.715439226344333</v>
       </c>
       <c r="P5" t="n">
-        <v>218.9744267494959</v>
+        <v>219.0460363628488</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23297,28 +23435,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4380164235011276</v>
+        <v>-0.4414536463194563</v>
       </c>
       <c r="J6" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K6" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3853796710352686</v>
+        <v>0.3915764612623133</v>
       </c>
       <c r="M6" t="n">
-        <v>3.157908872820539</v>
+        <v>3.153311303058855</v>
       </c>
       <c r="N6" t="n">
-        <v>17.51610669412642</v>
+        <v>17.46159726220217</v>
       </c>
       <c r="O6" t="n">
-        <v>4.185224808075</v>
+        <v>4.178707606689198</v>
       </c>
       <c r="P6" t="n">
-        <v>219.9323023346134</v>
+        <v>219.9690159055689</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23369,28 +23507,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009443013204845054</v>
+        <v>0.005710661639098444</v>
       </c>
       <c r="J7" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K7" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002886032438450536</v>
+        <v>0.0001066318554020507</v>
       </c>
       <c r="M7" t="n">
-        <v>3.216496230012884</v>
+        <v>3.214822150163669</v>
       </c>
       <c r="N7" t="n">
-        <v>17.68207801020116</v>
+        <v>17.63453041218236</v>
       </c>
       <c r="O7" t="n">
-        <v>4.205006303229658</v>
+        <v>4.199348808110892</v>
       </c>
       <c r="P7" t="n">
-        <v>225.834675641503</v>
+        <v>225.8745426834483</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23441,28 +23579,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.00825458353340401</v>
+        <v>-0.0143390886318392</v>
       </c>
       <c r="J8" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K8" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001603556885508839</v>
+        <v>0.0004871489850941657</v>
       </c>
       <c r="M8" t="n">
-        <v>3.014133761817564</v>
+        <v>3.014831509295559</v>
       </c>
       <c r="N8" t="n">
-        <v>24.32063941457496</v>
+        <v>24.3273049286907</v>
       </c>
       <c r="O8" t="n">
-        <v>4.93159603116222</v>
+        <v>4.932271781713848</v>
       </c>
       <c r="P8" t="n">
-        <v>213.9781293474637</v>
+        <v>214.0431254056799</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23513,28 +23651,28 @@
         <v>0.1106</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.113733800475109</v>
+        <v>-0.1148914492714734</v>
       </c>
       <c r="J9" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K9" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04224584605305226</v>
+        <v>0.04361264410357146</v>
       </c>
       <c r="M9" t="n">
-        <v>2.935594491670662</v>
+        <v>2.92326755681983</v>
       </c>
       <c r="N9" t="n">
-        <v>16.78756892015065</v>
+        <v>16.6924907449093</v>
       </c>
       <c r="O9" t="n">
-        <v>4.097263589293548</v>
+        <v>4.085644471183133</v>
       </c>
       <c r="P9" t="n">
-        <v>202.0500424743647</v>
+        <v>202.0624028336022</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23572,7 +23710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J479"/>
+  <dimension ref="A1:J482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48423,7 +48561,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>-46.89704925829206,168.13061122285117</t>
+          <t>-46.89704263906002,168.13076793670356</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -48462,6 +48600,162 @@
         </is>
       </c>
       <c r="J479" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:47+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>-46.8970434844331,168.13074792233132</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>-46.89783343661738,168.1290929140089</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>-46.89853559328795,168.12951889709566</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-46.89897198213746,168.12987593190033</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>-46.89956699119209,168.13048662942185</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>-46.89997236685746,168.1313837141609</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>-46.90024212209233,168.13219329065484</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>-46.90050621183846,168.13317891644905</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:43+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>-46.8970434844331,168.13074792233132</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>-46.8978331659742,168.12909932393637</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>-46.89853496594009,168.1295338103952</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-46.89896948429719,168.12987970088375</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>-46.89955525959842,168.13050435549016</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>-46.89996176009986,168.13139974544373</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>-46.9002308573716,168.13219726251256</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>-46.90049337524956,168.1331834423137</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>-46.897043965133875,168.13073654160968</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>-46.8978331659742,168.12909932393637</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>-46.89853496594009,168.1295338103952</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>-46.89896948429719,168.12987970088375</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>-46.89955525959842,168.13050435549016</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>-46.89996176009986,168.13139974544373</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-46.9002308573716,168.13219726251256</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-46.900490056947625,168.13318461226473</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0589/nzd0589.xlsx
+++ b/data/nzd0589/nzd0589.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J482"/>
+  <dimension ref="A1:J485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17788,6 +17788,114 @@
       <c r="J482" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>339.95</v>
+      </c>
+      <c r="C483" t="n">
+        <v>212.75</v>
+      </c>
+      <c r="D483" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="E483" t="n">
+        <v>216.45</v>
+      </c>
+      <c r="F483" t="n">
+        <v>204.73</v>
+      </c>
+      <c r="G483" t="n">
+        <v>221.47</v>
+      </c>
+      <c r="H483" t="n">
+        <v>207.15</v>
+      </c>
+      <c r="I483" t="n">
+        <v>196.27</v>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>341.47</v>
+      </c>
+      <c r="C484" t="n">
+        <v>213.32</v>
+      </c>
+      <c r="D484" t="n">
+        <v>241.04</v>
+      </c>
+      <c r="E484" t="n">
+        <v>217.44</v>
+      </c>
+      <c r="F484" t="n">
+        <v>205.88</v>
+      </c>
+      <c r="G484" t="n">
+        <v>222.57</v>
+      </c>
+      <c r="H484" t="n">
+        <v>208.4</v>
+      </c>
+      <c r="I484" t="n">
+        <v>196.87</v>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>341.47</v>
+      </c>
+      <c r="C485" t="n">
+        <v>213.37</v>
+      </c>
+      <c r="D485" t="n">
+        <v>241.13</v>
+      </c>
+      <c r="E485" t="n">
+        <v>217.86</v>
+      </c>
+      <c r="F485" t="n">
+        <v>205.87</v>
+      </c>
+      <c r="G485" t="n">
+        <v>222.57</v>
+      </c>
+      <c r="H485" t="n">
+        <v>208.68</v>
+      </c>
+      <c r="I485" t="n">
+        <v>197.08</v>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -17802,7 +17910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B518"/>
+  <dimension ref="A1:B521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22985,6 +23093,36 @@
       </c>
       <c r="B518" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -23147,28 +23285,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1511170470406395</v>
+        <v>0.1554117270875802</v>
       </c>
       <c r="J2" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K2" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002524696919292135</v>
+        <v>0.002705344411809141</v>
       </c>
       <c r="M2" t="n">
-        <v>15.52800827848677</v>
+        <v>15.44431353953606</v>
       </c>
       <c r="N2" t="n">
-        <v>520.9497071787575</v>
+        <v>517.7965796610711</v>
       </c>
       <c r="O2" t="n">
-        <v>22.82432271018699</v>
+        <v>22.75514402637503</v>
       </c>
       <c r="P2" t="n">
-        <v>333.2601692767869</v>
+        <v>333.2141455259964</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23219,28 +23357,28 @@
         <v>0.1473</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08525480415182972</v>
+        <v>0.08395266928460961</v>
       </c>
       <c r="J3" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K3" t="n">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03646561522399649</v>
+        <v>0.03583490027933756</v>
       </c>
       <c r="M3" t="n">
-        <v>2.618152461936709</v>
+        <v>2.607232108674001</v>
       </c>
       <c r="N3" t="n">
-        <v>11.09877136110579</v>
+        <v>11.03751364098887</v>
       </c>
       <c r="O3" t="n">
-        <v>3.331481856637642</v>
+        <v>3.32227537103547</v>
       </c>
       <c r="P3" t="n">
-        <v>211.9333795236228</v>
+        <v>211.9473318637238</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23291,28 +23429,28 @@
         <v>0.0717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.24261966435656</v>
+        <v>0.2384946878412773</v>
       </c>
       <c r="J4" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K4" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08737919735338762</v>
+        <v>0.08556536018449412</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3792305284438</v>
+        <v>4.368436420494634</v>
       </c>
       <c r="N4" t="n">
-        <v>35.2044419594378</v>
+        <v>35.0601808569975</v>
       </c>
       <c r="O4" t="n">
-        <v>5.933333123922657</v>
+        <v>5.921163809336599</v>
       </c>
       <c r="P4" t="n">
-        <v>237.5727338074621</v>
+        <v>237.617155630935</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23363,28 +23501,28 @@
         <v>0.141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1182872470367866</v>
+        <v>0.1123496089903555</v>
       </c>
       <c r="J5" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K5" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05522169789221987</v>
+        <v>0.05019554572481599</v>
       </c>
       <c r="M5" t="n">
-        <v>2.945688666238718</v>
+        <v>2.954402302694378</v>
       </c>
       <c r="N5" t="n">
-        <v>13.80448864465817</v>
+        <v>13.87274324018354</v>
       </c>
       <c r="O5" t="n">
-        <v>3.715439226344333</v>
+        <v>3.724613166515891</v>
       </c>
       <c r="P5" t="n">
-        <v>219.0460363628488</v>
+        <v>219.1096591617247</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23435,28 +23573,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4414536463194563</v>
+        <v>-0.4444542497017094</v>
       </c>
       <c r="J6" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K6" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3915764612623133</v>
+        <v>0.3974588125341477</v>
       </c>
       <c r="M6" t="n">
-        <v>3.153311303058855</v>
+        <v>3.14682923472024</v>
       </c>
       <c r="N6" t="n">
-        <v>17.46159726220217</v>
+        <v>17.39397856679067</v>
       </c>
       <c r="O6" t="n">
-        <v>4.178707606689198</v>
+        <v>4.170608896407175</v>
       </c>
       <c r="P6" t="n">
-        <v>219.9690159055689</v>
+        <v>220.0011659848941</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23507,28 +23645,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005710661639098444</v>
+        <v>0.001159471505718475</v>
       </c>
       <c r="J7" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K7" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001066318554020507</v>
+        <v>4.432627040640291e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.214822150163669</v>
+        <v>3.217021971228151</v>
       </c>
       <c r="N7" t="n">
-        <v>17.63453041218236</v>
+        <v>17.61599749662749</v>
       </c>
       <c r="O7" t="n">
-        <v>4.199348808110892</v>
+        <v>4.197141586440407</v>
       </c>
       <c r="P7" t="n">
-        <v>225.8745426834483</v>
+        <v>225.9233094123312</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23579,28 +23717,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0143390886318392</v>
+        <v>-0.02096913114370709</v>
       </c>
       <c r="J8" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K8" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004871489850941657</v>
+        <v>0.001046958949214694</v>
       </c>
       <c r="M8" t="n">
-        <v>3.014831509295559</v>
+        <v>3.01814887434211</v>
       </c>
       <c r="N8" t="n">
-        <v>24.3273049286907</v>
+        <v>24.36837041041444</v>
       </c>
       <c r="O8" t="n">
-        <v>4.932271781713848</v>
+        <v>4.936432964237885</v>
       </c>
       <c r="P8" t="n">
-        <v>214.0431254056799</v>
+        <v>214.1141676269718</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23651,28 +23789,28 @@
         <v>0.1106</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1148914492714734</v>
+        <v>-0.1175236256689194</v>
       </c>
       <c r="J9" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K9" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04361264410357146</v>
+        <v>0.04604763830869252</v>
       </c>
       <c r="M9" t="n">
-        <v>2.92326755681983</v>
+        <v>2.918560349157899</v>
       </c>
       <c r="N9" t="n">
-        <v>16.6924907449093</v>
+        <v>16.61957390111149</v>
       </c>
       <c r="O9" t="n">
-        <v>4.085644471183133</v>
+        <v>4.076711162335577</v>
       </c>
       <c r="P9" t="n">
-        <v>202.0624028336022</v>
+        <v>202.0906062219503</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23710,7 +23848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J482"/>
+  <dimension ref="A1:J485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48761,6 +48899,162 @@
         </is>
       </c>
     </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>-46.897045689016885,168.1306957279863</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>-46.89783329853419,168.12909618438005</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>-46.898535725360944,168.12951575745362</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-46.89897241925949,168.12987527232818</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>-46.8995624358396,168.13049351241736</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>-46.899974800172096,168.13138003639511</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>-46.900248147407964,168.13219116617205</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-46.90051180055735,168.13317694600383</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>-46.8970448491783,168.1307156115466</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>-46.89783298370409,168.12910364082623</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>-46.89853509801349,168.12953067075318</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-46.89896623710466,168.12988460056167</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>-46.89955525959842,168.13050435549016</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>-46.89996793697665,168.1313904095798</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>-46.90023723198103,168.13219501487237</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>-46.90050656113339,168.13317879329625</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>-46.8970448491783,168.1307156115466</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>-46.89783295608739,168.12910429490046</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>-46.89853504848597,168.12953184811894</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>-46.898963614372065,168.1298885579934</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>-46.899555322000516,168.1305042612026</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>-46.89996793697665,168.1313904095798</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>-46.90023478692537,168.132195876981</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>-46.90050472733498,168.1331794398485</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0589/nzd0589.xlsx
+++ b/data/nzd0589/nzd0589.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J485"/>
+  <dimension ref="A1:J487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17896,6 +17896,78 @@
       <c r="J485" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>340.66</v>
+      </c>
+      <c r="C486" t="n">
+        <v>213.65</v>
+      </c>
+      <c r="D486" t="n">
+        <v>242.93</v>
+      </c>
+      <c r="E486" t="n">
+        <v>219.69</v>
+      </c>
+      <c r="F486" t="n">
+        <v>206.21</v>
+      </c>
+      <c r="G486" t="n">
+        <v>222.57</v>
+      </c>
+      <c r="H486" t="n">
+        <v>208.32</v>
+      </c>
+      <c r="I486" t="n">
+        <v>196.04</v>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>340.39</v>
+      </c>
+      <c r="C487" t="n">
+        <v>213.09</v>
+      </c>
+      <c r="D487" t="n">
+        <v>241.19</v>
+      </c>
+      <c r="E487" t="n">
+        <v>219.54</v>
+      </c>
+      <c r="F487" t="n">
+        <v>206.25</v>
+      </c>
+      <c r="G487" t="n">
+        <v>222.67</v>
+      </c>
+      <c r="H487" t="n">
+        <v>208.26</v>
+      </c>
+      <c r="I487" t="n">
+        <v>196.18</v>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B521"/>
+  <dimension ref="A1:B523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23123,6 +23195,26 @@
       </c>
       <c r="B521" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -23285,28 +23377,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1554117270875802</v>
+        <v>0.1578501732254602</v>
       </c>
       <c r="J2" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K2" t="n">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002705344411809141</v>
+        <v>0.002815384172267565</v>
       </c>
       <c r="M2" t="n">
-        <v>15.44431353953606</v>
+        <v>15.38775736068601</v>
       </c>
       <c r="N2" t="n">
-        <v>517.7965796610711</v>
+        <v>515.7002045009392</v>
       </c>
       <c r="O2" t="n">
-        <v>22.75514402637503</v>
+        <v>22.70903354396525</v>
       </c>
       <c r="P2" t="n">
-        <v>333.2141455259964</v>
+        <v>333.1878941514142</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23357,28 +23449,28 @@
         <v>0.1473</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08395266928460961</v>
+        <v>0.08327084844321604</v>
       </c>
       <c r="J3" t="n">
+        <v>486</v>
+      </c>
+      <c r="K3" t="n">
         <v>484</v>
       </c>
-      <c r="K3" t="n">
-        <v>482</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.03583490027933756</v>
+        <v>0.03556964430347909</v>
       </c>
       <c r="M3" t="n">
-        <v>2.607232108674001</v>
+        <v>2.599225146442847</v>
       </c>
       <c r="N3" t="n">
-        <v>11.03751364098887</v>
+        <v>10.99526221066105</v>
       </c>
       <c r="O3" t="n">
-        <v>3.32227537103547</v>
+        <v>3.315910464813706</v>
       </c>
       <c r="P3" t="n">
-        <v>211.9473318637238</v>
+        <v>211.9546763142596</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23429,28 +23521,28 @@
         <v>0.0717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2384946878412773</v>
+        <v>0.2368725296375718</v>
       </c>
       <c r="J4" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K4" t="n">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08556536018449412</v>
+        <v>0.08515397843151096</v>
       </c>
       <c r="M4" t="n">
-        <v>4.368436420494634</v>
+        <v>4.3567691017418</v>
       </c>
       <c r="N4" t="n">
-        <v>35.0601808569975</v>
+        <v>34.9356781752394</v>
       </c>
       <c r="O4" t="n">
-        <v>5.921163809336599</v>
+        <v>5.910641096804931</v>
       </c>
       <c r="P4" t="n">
-        <v>237.617155630935</v>
+        <v>237.6347167822949</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23501,28 +23593,28 @@
         <v>0.141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1123496089903555</v>
+        <v>0.1103362256956159</v>
       </c>
       <c r="J5" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K5" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05019554572481599</v>
+        <v>0.04882392680103798</v>
       </c>
       <c r="M5" t="n">
-        <v>2.954402302694378</v>
+        <v>2.95137575644925</v>
       </c>
       <c r="N5" t="n">
-        <v>13.87274324018354</v>
+        <v>13.84205710737206</v>
       </c>
       <c r="O5" t="n">
-        <v>3.724613166515891</v>
+        <v>3.720491514218526</v>
       </c>
       <c r="P5" t="n">
-        <v>219.1096591617247</v>
+        <v>219.1313381774837</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23573,28 +23665,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4444542497017094</v>
+        <v>-0.4457896821290493</v>
       </c>
       <c r="J6" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K6" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3974588125341477</v>
+        <v>0.400878104821582</v>
       </c>
       <c r="M6" t="n">
-        <v>3.14682923472024</v>
+        <v>3.13960521999622</v>
       </c>
       <c r="N6" t="n">
-        <v>17.39397856679067</v>
+        <v>17.33401058438005</v>
       </c>
       <c r="O6" t="n">
-        <v>4.170608896407175</v>
+        <v>4.163413333357625</v>
       </c>
       <c r="P6" t="n">
-        <v>220.0011659848941</v>
+        <v>220.0155445254947</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23645,28 +23737,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001159471505718475</v>
+        <v>-0.001472646845632332</v>
       </c>
       <c r="J7" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K7" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L7" t="n">
-        <v>4.432627040640291e-06</v>
+        <v>7.196125848651924e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.217021971228151</v>
+        <v>3.216388953619661</v>
       </c>
       <c r="N7" t="n">
-        <v>17.61599749662749</v>
+        <v>17.58861025838004</v>
       </c>
       <c r="O7" t="n">
-        <v>4.197141586440407</v>
+        <v>4.193877711424124</v>
       </c>
       <c r="P7" t="n">
-        <v>225.9233094123312</v>
+        <v>225.951649382724</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23717,28 +23809,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02096913114370709</v>
+        <v>-0.02512094332291082</v>
       </c>
       <c r="J8" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K8" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001046958949214694</v>
+        <v>0.00150839018806892</v>
       </c>
       <c r="M8" t="n">
-        <v>3.01814887434211</v>
+        <v>3.019847857774292</v>
       </c>
       <c r="N8" t="n">
-        <v>24.36837041041444</v>
+        <v>24.38028545867974</v>
       </c>
       <c r="O8" t="n">
-        <v>4.936432964237885</v>
+        <v>4.937639664726431</v>
       </c>
       <c r="P8" t="n">
-        <v>214.1141676269718</v>
+        <v>214.1588710616599</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23789,28 +23881,28 @@
         <v>0.1106</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1175236256689194</v>
+        <v>-0.1197253814704047</v>
       </c>
       <c r="J9" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K9" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04604763830869252</v>
+        <v>0.04802605624352052</v>
       </c>
       <c r="M9" t="n">
-        <v>2.918560349157899</v>
+        <v>2.917603117165253</v>
       </c>
       <c r="N9" t="n">
-        <v>16.61957390111149</v>
+        <v>16.5827583895139</v>
       </c>
       <c r="O9" t="n">
-        <v>4.076711162335577</v>
+        <v>4.072193314359462</v>
       </c>
       <c r="P9" t="n">
-        <v>202.0906062219503</v>
+        <v>202.114312230529</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23848,7 +23940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J485"/>
+  <dimension ref="A1:J487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49055,6 +49147,110 @@
         </is>
       </c>
     </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>-46.89704529672431,168.130705015702</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>-46.897832801433836,168.12910795771612</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>-46.89853405793312,168.12955539543364</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>-46.89895218674963,168.12990580108433</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>-46.899553200328995,168.13050746698005</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>-46.89996793697665,168.1313904095798</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>-46.90023793056835,168.1321947685556</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>-46.900513809003186,168.13317623787498</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>-46.89704544590609,168.1307014837538</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>-46.897833110740855,168.12910063208483</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>-46.898535015467615,168.12953263302944</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-46.8989531234401,168.12990438771652</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>-46.89955295072058,168.13050784413036</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>-46.89996731304974,168.13139135259644</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>-46.90023845450885,168.132194583818</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>-46.900512586470946,168.13317666890995</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
